--- a/artfynd/A 27700-2024 artfynd.xlsx
+++ b/artfynd/A 27700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119170727</v>
+        <v>119170659</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579597</v>
+        <v>579506</v>
       </c>
       <c r="R2" t="n">
-        <v>6397827</v>
+        <v>6397817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119170659</v>
+        <v>119170727</v>
       </c>
       <c r="B3" t="n">
-        <v>94679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,27 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579506</v>
+        <v>579597</v>
       </c>
       <c r="R3" t="n">
-        <v>6397817</v>
+        <v>6397827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,16 +889,11 @@
         <v>119170693</v>
       </c>
       <c r="B4" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1008,6 +993,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119170756</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 27700, Kammartorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579544</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6397879</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
